--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:28</t>
+    <t xml:space="preserve">2026-09-09 23:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:25</t>
+    <t xml:space="preserve">2026-09-17 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:20</t>
+    <t xml:space="preserve">2026-09-23 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:48</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -159,7 +159,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1181,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-02 11:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:21</t>
+    <t xml:space="preserve">2026-10-02 15:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:07</t>
+    <t xml:space="preserve">2026-10-05 12:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
